--- a/etc/sample_data/mapping.xlsx
+++ b/etc/sample_data/mapping.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sijinzhang/Github/Syspop_v2/etc/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02C7A24-2F18-E444-BC89-C13BD0091ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D795307-7445-564E-98F5-992B39F66D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17560" yWindow="1540" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{E9F76472-E11C-4242-9B4B-090DCA1B26D4}"/>
+    <workbookView xWindow="10360" yWindow="1540" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{E9F76472-E11C-4242-9B4B-090DCA1B26D4}"/>
   </bookViews>
   <sheets>
     <sheet name="ethnicity" sheetId="1" r:id="rId1"/>
     <sheet name="occupation" sheetId="9" r:id="rId2"/>
-    <sheet name="age" sheetId="2" r:id="rId3"/>
-    <sheet name="gender" sheetId="3" r:id="rId4"/>
-    <sheet name="industry" sheetId="4" r:id="rId5"/>
-    <sheet name="work_status" sheetId="5" r:id="rId6"/>
-    <sheet name="income" sheetId="6" r:id="rId7"/>
-    <sheet name="travel_to_work" sheetId="7" r:id="rId8"/>
-    <sheet name="work_hours" sheetId="8" r:id="rId9"/>
+    <sheet name="location" sheetId="10" r:id="rId3"/>
+    <sheet name="age" sheetId="2" r:id="rId4"/>
+    <sheet name="gender" sheetId="3" r:id="rId5"/>
+    <sheet name="industry" sheetId="4" r:id="rId6"/>
+    <sheet name="work_status" sheetId="5" r:id="rId7"/>
+    <sheet name="income" sheetId="6" r:id="rId8"/>
+    <sheet name="travel_to_work" sheetId="7" r:id="rId9"/>
+    <sheet name="work_hours" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="117">
   <si>
     <t>code</t>
   </si>
@@ -386,6 +387,15 @@
   </si>
   <si>
     <t>Labourers</t>
+  </si>
+  <si>
+    <t>Wellington</t>
+  </si>
+  <si>
+    <t>Auckland</t>
+  </si>
+  <si>
+    <t>Canterbury</t>
   </si>
 </sst>
 </file>
@@ -1117,6 +1127,88 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F45B4B9-E534-2443-BB32-6BD22A256BF9}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6E1DB6-8C40-6543-9209-613E7685E690}">
   <dimension ref="A1:B10"/>
@@ -1208,6 +1300,48 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0D5150-9BC3-5844-9575-5C94B6204824}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D55A3AF8-FEF7-744C-BB1C-435C930C5E26}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1257,7 +1391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE416B9-4551-C549-8440-6B69ED1EA950}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1299,7 +1433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2313084B-35E0-5141-AE80-F3FEA2E59A7C}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1437,7 +1571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6193E08B-E061-2343-8039-B3B57C60B66A}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1471,7 +1605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D447F826-00B8-CD4C-863E-29718A6DCA58}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1545,7 +1679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6ECA67-CB57-2A4B-BF53-A0ECC2981916}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1649,86 +1783,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F45B4B9-E534-2443-BB32-6BD22A256BF9}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>